--- a/exports/Laporan_Kesesuaian_RPS_BAP.xlsx
+++ b/exports/Laporan_Kesesuaian_RPS_BAP.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>22 July 2026 23:29</t>
+          <t>23 July 2026 12:29</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>14.29%</t>
         </is>
       </c>
     </row>
@@ -616,12 +616,12 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Kontrak Kuliah</t>
+          <t>Kontrak Kuliah, Konsep dasar OOP</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>kontrakuliah</t>
+          <t>Kontrak Kuliah, Konsep dasar OOP</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -631,12 +631,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>92.31%</t>
+          <t>100.00%</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 92.31%. Kata kunci cocok: []</t>
+          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: ['dasar']</t>
         </is>
       </c>
     </row>
@@ -651,36 +651,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Classes and object</t>
+          <t>Classes and Object</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Classes and object
-1. The difference
-between
-2. class and object,
-by giving
-3. some examples
-4. making a simple
-first object
-(Fokus: firstprogramming
-with java)
-5. rimitive and
-reference: Type,
-keywords,
-reference
-variable, object
-declaration &amp;
-assignment,
-objects in
-garbage
-collector, arrays
-6. Object cycle: life
-and death
-7. Constructor &amp;
-Garbage
-collector</t>
+          <t>Classes and Object</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -695,7 +671,7 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: ['and', 'object']</t>
+          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: ['and']</t>
         </is>
       </c>
     </row>
@@ -710,17 +686,17 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Konsep enkapsulasi</t>
+          <t>Konsep Enkapsulasi</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Komponen dalam enkapsulasi : 1. modifier 2. construct</t>
+          <t>GUI &amp; Swing</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>TIDAK_SESUAI</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -730,7 +706,7 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: ['enkapsulasi']</t>
+          <t>Materi diacak. Cocok dengan pertemuan ke-14 (skor=100.00%)</t>
         </is>
       </c>
     </row>
@@ -745,29 +721,27 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>1. Mencoba</t>
+          <t>Mencoba program</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>1. Mencoba
-program pada
-buku referensi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -782,27 +756,27 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>1. Mendesain</t>
+          <t>Mendesain program</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>program yang memanfaatkan enkapsulasi untuk perma</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -817,27 +791,27 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Konsep Pewarisan :</t>
+          <t>Konsep Pewarisan</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>• Pewarisan tunggal • Pewarisan Majemuk</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -852,32 +826,27 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Konsep Pewarisan :</t>
+          <t>Overriding &amp; Overloading</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>• Pewarisan
-tunggal
-• Pewarisan
-Majemuk
-1. Overriding
-2. Overloading</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -892,35 +861,27 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>1. Exception</t>
+          <t>Exception Handling</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Exception
-handling
-2. Exception as an
-object
-3. try-catch
-4. throws
-5. Try-catch- finally
-6. Multiple
-exception</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -940,33 +901,22 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Object Persistence
-1. Saving object
-state
-2. Writing a
-serialized object
-to a file
-3. Object
-serialization
-(serializable
-interface)
-4. Deserializing an
-object</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -986,27 +936,22 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Multithreading
-1. Launching new
-thread
-2. Runnable
-interface
-3. Thread' state</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -1021,30 +966,27 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Using java library</t>
+          <t>Using Java Library</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Using java library
-(java API)
-1. How to use it
-2. Simple example</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: ['java', 'library']</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -1064,18 +1006,12 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Collections
-1. Interface
-Collection and
-class Collections
-2. Type wrapper
-classess for
-primitive types</t>
+          <t>Mencoba program</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>TIDAK_SESUAI</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1085,7 +1021,7 @@
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi diacak. Cocok dengan pertemuan ke-4 (skor=100.00%)</t>
         </is>
       </c>
     </row>
@@ -1100,30 +1036,27 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Making connection</t>
+          <t>Making Connection with Database</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Making connection
-with database
-1. JDBC
-2. Oracle/mysql (?)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: ['connection']</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
@@ -1138,34 +1071,27 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>GUI &amp; SWING</t>
+          <t>GUI &amp; Swing</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>GUI &amp; SWING
-1. User event
-2. Listener
-interface
-3. Action event
-4. Inner class
-5. Swing
-component</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>SESUAI</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>100.00%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>Materi sesuai dengan skor 100.00%. Kata kunci cocok: []</t>
+          <t>Materi belum diajarkan (BAP belum diinput)</t>
         </is>
       </c>
     </row>
